--- a/p/content_tmp.xlsx
+++ b/p/content_tmp.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adsv\private\books\language\ingush\Dahkilgov\github\dahkilgov\p\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F34CFE7-E0E3-4CE8-A50C-1EF41D2B9997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{532D0350-E222-4911-A2FA-A55EA55406AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-2415" windowWidth="38640" windowHeight="21120" xr2:uid="{AC639D1C-64A7-45F6-9CFA-A1A688E9895B}"/>
   </bookViews>
@@ -422,9 +422,6 @@
     <t>Глагол, времена, прошедшее очевидное время, отрицательная форма, частица -нзар.</t>
   </si>
   <si>
-    <t xml:space="preserve">Прилагательное, качественное, самостоятельное. TODO </t>
-  </si>
-  <si>
     <t>Существительное, классы, общие сведения.</t>
   </si>
   <si>
@@ -434,9 +431,6 @@
     <t>Существительное, падежи, склонение по падежам слова "саг".</t>
   </si>
   <si>
-    <t>Существительное, падежи, склонение личных имен. TODO</t>
-  </si>
-  <si>
     <t>Существительное, множественное число.</t>
   </si>
   <si>
@@ -624,6 +618,12 @@
   </si>
   <si>
     <t>Масдар, общие сведения.</t>
+  </si>
+  <si>
+    <t>Морфология. Номинизирующий суффикс "лга".</t>
+  </si>
+  <si>
+    <t>Краткий обзор грамматики.</t>
   </si>
 </sst>
 </file>
@@ -1042,13 +1042,13 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -1056,13 +1056,13 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -1070,13 +1070,13 @@
         <v>144</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -1084,13 +1084,13 @@
         <v>105</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -1098,13 +1098,13 @@
         <v>62</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -1112,13 +1112,13 @@
         <v>27</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -1126,83 +1126,83 @@
         <v>152</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>166</v>
+        <v>48</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>48</v>
+        <v>166</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>192</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -1210,52 +1210,52 @@
         <v>9</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>7</v>
+        <v>124</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>192</v>
+        <v>168</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>169</v>
@@ -1263,16 +1263,16 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>66</v>
+        <v>7</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -1280,27 +1280,27 @@
         <v>38</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>128</v>
+        <v>66</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -1308,13 +1308,13 @@
         <v>70</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -1322,13 +1322,13 @@
         <v>14</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -1336,111 +1336,111 @@
         <v>88</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>160</v>
+        <v>40</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>111</v>
+        <v>29</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>30</v>
+        <v>160</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>24</v>
+        <v>111</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>147</v>
+        <v>23</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>23</v>
+        <v>165</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>19</v>
+        <v>137</v>
       </c>
       <c r="C26" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>171</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>18</v>
+        <v>137</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>15</v>
+        <v>99</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>69</v>
+        <v>18</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>171</v>
+        <v>69</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>117</v>
+        <v>69</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
@@ -1451,232 +1451,232 @@
         <v>100</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>165</v>
+        <v>28</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>139</v>
+        <v>22</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>29</v>
+        <v>140</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>117</v>
+        <v>30</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>22</v>
+        <v>193</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>3</v>
+        <v>131</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>192</v>
+        <v>169</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>49</v>
+        <v>127</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>114</v>
+        <v>58</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>132</v>
+        <v>58</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>141</v>
+        <v>51</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>134</v>
+        <v>42</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>98</v>
+        <v>141</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>155</v>
+        <v>53</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>107</v>
+        <v>44</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>20</v>
+        <v>155</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -1687,7 +1687,7 @@
         <v>116</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
@@ -1695,10 +1695,10 @@
         <v>154</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
@@ -1709,7 +1709,7 @@
         <v>84</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
@@ -1720,7 +1720,7 @@
         <v>85</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
@@ -1731,7 +1731,7 @@
         <v>86</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
@@ -1742,7 +1742,7 @@
         <v>89</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
@@ -1753,7 +1753,7 @@
         <v>90</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
@@ -1764,7 +1764,7 @@
         <v>91</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
@@ -1775,7 +1775,7 @@
         <v>113</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
@@ -1786,7 +1786,7 @@
         <v>112</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
@@ -1797,7 +1797,7 @@
         <v>83</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
@@ -1808,7 +1808,7 @@
         <v>82</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
@@ -1819,7 +1819,7 @@
         <v>115</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
@@ -1830,7 +1830,7 @@
         <v>20</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
@@ -1841,7 +1841,7 @@
         <v>53</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
@@ -1849,10 +1849,10 @@
         <v>134</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
@@ -1863,7 +1863,7 @@
         <v>11</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
@@ -1874,10 +1874,10 @@
         <v>17</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
@@ -1888,10 +1888,10 @@
         <v>47</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
@@ -1902,24 +1902,24 @@
         <v>48</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>94</v>
+        <v>134</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
@@ -1930,175 +1930,175 @@
         <v>87</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>127</v>
+        <v>79</v>
       </c>
       <c r="C72" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D72" s="3" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>136</v>
+        <v>6</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76">
-        <v>77</v>
+        <v>142</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77">
-        <v>74</v>
+        <v>13</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>192</v>
+        <v>167</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80">
-        <v>107</v>
+        <v>164</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>54</v>
+        <v>114</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81">
-        <v>164</v>
+        <v>45</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>114</v>
+        <v>38</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
@@ -2109,80 +2109,80 @@
         <v>46</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>192</v>
+        <v>170</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88">
+        <v>44</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B88" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="C88" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
@@ -2193,584 +2193,584 @@
         <v>110</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90">
-        <v>25</v>
+        <v>140</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91">
-        <v>31</v>
+        <v>112</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92">
-        <v>112</v>
+        <v>54</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>192</v>
+        <v>167</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95">
-        <v>42</v>
+        <v>108</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>30</v>
+        <v>124</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96">
-        <v>108</v>
+        <v>46</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>124</v>
+        <v>39</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97">
-        <v>46</v>
+        <v>110</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98">
-        <v>110</v>
+        <v>64</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101">
-        <v>60</v>
+        <v>168</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>51</v>
+        <v>118</v>
       </c>
       <c r="C101" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D101" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="D101" s="3" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102">
-        <v>168</v>
+        <v>136</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103">
-        <v>136</v>
+        <v>65</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>119</v>
+        <v>67</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>67</v>
+        <v>125</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>126</v>
+        <v>65</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108">
-        <v>76</v>
+        <v>153</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110">
-        <v>146</v>
+        <v>115</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112">
-        <v>87</v>
+        <v>130</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114">
-        <v>139</v>
+        <v>61</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>101</v>
+        <v>52</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="D115" s="3" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116">
-        <v>97</v>
+        <v>26</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>88</v>
+        <v>35</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>77</v>
+        <v>31</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120">
-        <v>41</v>
+        <v>119</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121">
-        <v>119</v>
+        <v>59</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125">
-        <v>50</v>
+        <v>159</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>41</v>
+        <v>122</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126">
-        <v>159</v>
+        <v>103</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>122</v>
+        <v>93</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127">
-        <v>103</v>
+        <v>148</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128">
-        <v>148</v>
+        <v>72</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A129">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>192</v>
+        <v>167</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130">
-        <v>121</v>
+        <v>157</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>63</v>
+        <v>109</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131">
-        <v>157</v>
+        <v>81</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>109</v>
+        <v>1</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133">
+        <v>85</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="C133" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D133" s="3" t="s">
         <v>171</v>
@@ -2778,41 +2778,41 @@
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134">
-        <v>85</v>
+        <v>161</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135">
-        <v>109</v>
+        <v>32</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A136">
-        <v>161</v>
+        <v>121</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D136" s="3" t="s">
         <v>174</v>
@@ -2820,44 +2820,44 @@
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A137">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138">
-        <v>29</v>
+        <v>84</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>192</v>
+        <v>167</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A139">
-        <v>150</v>
+        <v>86</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.3">
@@ -2868,248 +2868,248 @@
         <v>57</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A142">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>2</v>
+        <v>92</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A143">
-        <v>84</v>
+        <v>156</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A144">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A145">
-        <v>145</v>
+        <v>118</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>103</v>
+        <v>60</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A146">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A147">
-        <v>133</v>
+        <v>95</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>97</v>
+        <v>3</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A148">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A149">
-        <v>102</v>
+        <v>135</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C149" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D149" s="3" t="s">
         <v>178</v>
-      </c>
-      <c r="D149" s="3" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A150">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>98</v>
+        <v>192</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A151">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>192</v>
+        <v>167</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A152">
-        <v>143</v>
+        <v>6</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>193</v>
+        <v>10</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A153">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A154">
-        <v>120</v>
+        <v>19</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A155">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>192</v>
+        <v>169</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A156">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A157">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.3">
@@ -3120,21 +3120,21 @@
         <v>36</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A159">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D159" s="3" t="s">
         <v>173</v>
@@ -3142,30 +3142,30 @@
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A160">
-        <v>22</v>
+        <v>120</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A161">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>170</v>
+        <v>190</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.3">
@@ -3176,52 +3176,52 @@
         <v>68</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A163">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>40</v>
+        <v>153</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A164">
-        <v>169</v>
+        <v>47</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>192</v>
+        <v>168</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.3">
@@ -3229,24 +3229,24 @@
         <v>132</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A167">
-        <v>67</v>
+        <v>129</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D167" s="3" t="s">
         <v>170</v>
@@ -3254,41 +3254,41 @@
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A168">
-        <v>47</v>
+        <v>127</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A169">
-        <v>122</v>
+        <v>169</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A170">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D170" s="3" t="s">
         <v>173</v>
@@ -3296,16 +3296,16 @@
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A171">
-        <v>129</v>
+        <v>171</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>138</v>
+        <v>194</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
